--- a/src/assets/excels/抽奖结果.xlsx
+++ b/src/assets/excels/抽奖结果.xlsx
@@ -1,33 +1,139 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="抽奖结果" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="数据表" state="visible" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
+  <si>
+    <t>奖项</t>
+  </si>
+  <si>
+    <t>工号</t>
+  </si>
+  <si>
+    <t>姓名</t>
+  </si>
+  <si>
+    <t>部门</t>
+  </si>
+  <si>
+    <t>十人奖</t>
+  </si>
+  <si>
+    <t>000005</t>
+  </si>
+  <si>
+    <t>徐阶</t>
+  </si>
+  <si>
+    <t>内阁 户部</t>
+  </si>
+  <si>
+    <t>000028</t>
+  </si>
+  <si>
+    <t>张知良</t>
+  </si>
+  <si>
+    <t>建德县</t>
+  </si>
+  <si>
+    <t>000018</t>
+  </si>
+  <si>
+    <t>何茂才</t>
+  </si>
+  <si>
+    <t>浙江布政使司 浙江按察使司</t>
+  </si>
+  <si>
+    <t>000024</t>
+  </si>
+  <si>
+    <t>周云逸</t>
+  </si>
+  <si>
+    <t>钦天监</t>
+  </si>
+  <si>
+    <t>000007</t>
+  </si>
+  <si>
+    <t>高拱</t>
+  </si>
+  <si>
+    <t>000034</t>
+  </si>
+  <si>
+    <t>徐千户</t>
+  </si>
+  <si>
+    <t>浙江按察使司</t>
+  </si>
+  <si>
+    <t>000022</t>
+  </si>
+  <si>
+    <t>杨金水</t>
+  </si>
+  <si>
+    <t>浙江市舶司</t>
+  </si>
+  <si>
+    <t>000015</t>
+  </si>
+  <si>
+    <t>王用汲</t>
+  </si>
+  <si>
+    <t>昆山县 建德县</t>
+  </si>
+  <si>
+    <t>000037</t>
+  </si>
+  <si>
+    <t>鄢懋卿</t>
+  </si>
+  <si>
+    <t>刑部</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="4F81BD"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -42,14 +148,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -374,272 +489,170 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>工号</v>
-      </c>
-      <c r="B1" t="str">
-        <v>姓名</v>
-      </c>
-      <c r="C1" t="str">
-        <v>部门</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>特别奖</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>特等奖</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>一等奖</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>二等奖</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>三等奖</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>四等奖</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>五等奖</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>000108</v>
-      </c>
-      <c r="B9" t="str">
-        <v>贾蓉</v>
-      </c>
-      <c r="C9" t="str">
-        <v>红楼梦</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>000060</v>
-      </c>
-      <c r="B10" t="str">
-        <v>西蒙</v>
-      </c>
-      <c r="C10" t="str">
-        <v>ATP</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>000066</v>
-      </c>
-      <c r="B11" t="str">
-        <v>索萨</v>
-      </c>
-      <c r="C11" t="str">
-        <v>ATP</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>000086</v>
-      </c>
-      <c r="B12" t="str">
-        <v>王熙凤</v>
-      </c>
-      <c r="C12" t="str">
-        <v>红楼梦</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>000005</v>
-      </c>
-      <c r="B13" t="str">
-        <v>卡普</v>
-      </c>
-      <c r="C13" t="str">
-        <v>WTA</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>000207</v>
-      </c>
-      <c r="B14" t="str">
-        <v>药官</v>
-      </c>
-      <c r="C14" t="str">
-        <v>红楼梦</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>000026</v>
-      </c>
-      <c r="B15" t="str">
-        <v>谢淑薇</v>
-      </c>
-      <c r="C15" t="str">
-        <v>WTA</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>000095</v>
-      </c>
-      <c r="B16" t="str">
-        <v>紫鹃</v>
-      </c>
-      <c r="C16" t="str">
-        <v>红楼梦</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>六等奖</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>000050</v>
-      </c>
-      <c r="B18" t="str">
-        <v>伊斯内尔</v>
-      </c>
-      <c r="C18" t="str">
-        <v>ATP</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>000070</v>
-      </c>
-      <c r="B19" t="str">
-        <v>布莱恩</v>
-      </c>
-      <c r="C19" t="str">
-        <v>ATP</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>000011</v>
-      </c>
-      <c r="B20" t="str">
-        <v>大威</v>
-      </c>
-      <c r="C20" t="str">
-        <v>WTA</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>000200</v>
-      </c>
-      <c r="B21" t="str">
-        <v>琪官</v>
-      </c>
-      <c r="C21" t="str">
-        <v>红楼梦</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>000307</v>
-      </c>
-      <c r="B22" t="str">
-        <v>阿姆</v>
-      </c>
-      <c r="C22" t="str">
-        <v>MUSIC</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>000203</v>
-      </c>
-      <c r="B23" t="str">
-        <v>宝官</v>
-      </c>
-      <c r="C23" t="str">
-        <v>红楼梦</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>000067</v>
-      </c>
-      <c r="B24" t="str">
-        <v>哈赛</v>
-      </c>
-      <c r="C24" t="str">
-        <v>ATP</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>000308</v>
-      </c>
-      <c r="B25" t="str">
-        <v>火星哥</v>
-      </c>
-      <c r="C25" t="str">
-        <v>MUSIC</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>000302</v>
-      </c>
-      <c r="B26" t="str">
-        <v>阿黛尔</v>
-      </c>
-      <c r="C26" t="str">
-        <v>MUSIC</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>000201</v>
-      </c>
-      <c r="B27" t="str">
-        <v>碧昂丝</v>
-      </c>
-      <c r="C27" t="str">
-        <v>MUSIC</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>000104</v>
-      </c>
-      <c r="B28" t="str">
-        <v>贾敬</v>
-      </c>
-      <c r="C28" t="str">
-        <v>红楼梦</v>
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C28"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/src/assets/excels/抽奖结果.xlsx
+++ b/src/assets/excels/抽奖结果.xlsx
@@ -1,12 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codes\private\party-lottery\src\assets\excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView windowHeight="17680"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="数据表" state="visible" r:id="rId4"/>
+    <sheet name="数据表" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -109,21 +130,182 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
-    <font>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFF"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -132,11 +314,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="4F81BD"/>
+        <fgColor rgb="FF4F81BD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -144,25 +513,311 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -484,20 +1139,20 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -511,7 +1166,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -525,7 +1180,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -539,7 +1194,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -553,7 +1208,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -567,7 +1222,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -581,7 +1236,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -595,7 +1250,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -609,7 +1264,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -623,7 +1278,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -637,7 +1292,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -653,6 +1308,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>